--- a/data/lekplatskontroll.xlsx
+++ b/data/lekplatskontroll.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75741EDF-346D-4A1F-AD38-2885EAB38BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85368D10-49FD-4618-AC34-EE2B75724B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lekplatsmatris" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t>Lekplats</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>Gångytan är fri från halkrisk och snubbelrisk</t>
+  </si>
+  <si>
+    <t>Räcken, stolpar och ledstänger är fast förankrade och svajar inte när man lutar sig mot dem.</t>
   </si>
   <si>
     <t>Räcken och skydd sitter stadigt</t>
@@ -1669,7 +1672,7 @@
       <c r="Z5" s="15"/>
       <c r="AA5" s="15"/>
     </row>
-    <row r="6" spans="1:27" s="40" customFormat="1" ht="28.5">
+    <row r="6" spans="1:27" s="40" customFormat="1" ht="72">
       <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
@@ -1706,7 +1709,7 @@
     </row>
     <row r="7" spans="1:27" s="40" customFormat="1" ht="28.5">
       <c r="A7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>

--- a/data/lekplatskontroll.xlsx
+++ b/data/lekplatskontroll.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orebrokommun-my.sharepoint.com/personal/mimmi_beckman_orebro_se/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2699CD7-6BB3-4517-9604-A4EA5DB1E973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{082FFA92-712D-4D65-A6DC-D1B3836D4844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="105">
   <si>
     <t>Lekplats</t>
   </si>
@@ -82,271 +82,274 @@
     <t>Stock-element för fysisk lek</t>
   </si>
   <si>
+    <t>Träd</t>
+  </si>
+  <si>
+    <t>Portaler</t>
+  </si>
+  <si>
+    <t>Lundbyparken</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Öknaskogen</t>
+  </si>
+  <si>
+    <t>Hjärstaskogen</t>
+  </si>
+  <si>
+    <t>Japanska dammen (Hjärstaskogen)</t>
+  </si>
+  <si>
+    <t>Baronbackarna</t>
+  </si>
+  <si>
+    <t>Tjäderleken, Björkhaga</t>
+  </si>
+  <si>
+    <t>VOX-parken</t>
+  </si>
+  <si>
+    <t>Militärförråden (Varberga)</t>
+  </si>
+  <si>
+    <t>Myrans lekplats (Varberga)</t>
+  </si>
+  <si>
+    <t>Fantasigläntan (Varberga)</t>
+  </si>
+  <si>
+    <t>Groddammen (Varberga)</t>
+  </si>
+  <si>
+    <t>Östra Rostas cykellek</t>
+  </si>
+  <si>
+    <t>Östra Rostas vattenlek</t>
+  </si>
+  <si>
+    <t>Sköldpaddsleken (Östra Rosta)</t>
+  </si>
+  <si>
+    <t>Bråtenvägen, Lillån</t>
+  </si>
+  <si>
+    <t>Norrbyparken</t>
+  </si>
+  <si>
+    <t>Ringstorp (solrosparken)</t>
+  </si>
+  <si>
+    <t>Sofiaparken</t>
+  </si>
+  <si>
+    <t>Stora holmen</t>
+  </si>
+  <si>
+    <t>Stadsparken</t>
+  </si>
+  <si>
+    <t>Eklunden</t>
+  </si>
+  <si>
+    <t>Hagen</t>
+  </si>
+  <si>
+    <t>Lergöken (Sörbyängen)</t>
+  </si>
+  <si>
+    <t>Tybble naturlek</t>
+  </si>
+  <si>
+    <t>Tybbleparken</t>
+  </si>
+  <si>
+    <t>Hjälmarsviksparken</t>
+  </si>
+  <si>
+    <t>Äventyrsstigen (Saxons)</t>
+  </si>
+  <si>
+    <t>Äventyrstrappan (Saxons)</t>
+  </si>
+  <si>
+    <t>Tallebacka-Majas väg</t>
+  </si>
+  <si>
+    <t>Vänneboparken</t>
+  </si>
+  <si>
+    <t>Brunnsparken</t>
+  </si>
+  <si>
+    <t>Mariebergs skogslek</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>Fästen för vajrar runt träden är i gott skick.</t>
+  </si>
+  <si>
+    <t>Fundament för master utan anmärkning.</t>
+  </si>
+  <si>
+    <t>Det finns inte problem med exponerad ståltråd som sticker fram.</t>
+  </si>
+  <si>
+    <t>Stommar är i gott skick.</t>
+  </si>
+  <si>
+    <t>Trä och andra material är i gott skick.</t>
+  </si>
+  <si>
+    <t>Fundament eller förankring i marken är i gott skick. Det finns inga tecken på att strukturen skulle kunna rasa eller välta.</t>
+  </si>
+  <si>
+    <t>Det finns inga uppenbara problem med erosion.</t>
+  </si>
+  <si>
+    <t>Trappsteg eller ramper intill rutschkanor är väl förankrade och kräver inga åtgärder.</t>
+  </si>
+  <si>
+    <t>Element som är delvis nergrävda har en god förankring. De sitter inte löst eller går att rubba.</t>
+  </si>
+  <si>
+    <t>Det står inga döda träd eller andra riskträd intill lekelement</t>
+  </si>
+  <si>
+    <t>Inga problem med att fästen runt träd växer in i barken eller har för högt tryck.</t>
+  </si>
+  <si>
+    <t>Kättingar i lianer är inte slitna</t>
+  </si>
+  <si>
+    <t>Det finns inga exponerade skruvar eller liknande som däck är fästa med (i varandra eller till annat).</t>
+  </si>
+  <si>
+    <t>Det finns inga problem med röta eller minskad hållfasthet.</t>
+  </si>
+  <si>
+    <t>Förankringen är god och kräver inga åtgärder.</t>
+  </si>
+  <si>
+    <t>Trappsteg är väl förankrade.</t>
+  </si>
+  <si>
+    <t>Stockar och andra träelement är i gott skick. Det finns inte problem med röta.</t>
+  </si>
+  <si>
+    <t>Vajrar är bra spända.</t>
+  </si>
+  <si>
+    <t>Fästen av lianer och andra metallfästen är i gott skick.</t>
+  </si>
+  <si>
+    <t>Det samlas inte vatten inne i däck som är förankrade.</t>
+  </si>
+  <si>
+    <t>Stommar bedöms hålla i ett år till utan problem.</t>
+  </si>
+  <si>
+    <t>Det finns inga trasiga eller lösa delar som behöver åtgärdas.</t>
+  </si>
+  <si>
+    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet nedanför strukturen.</t>
+  </si>
+  <si>
+    <t>Vajrar är i gott skick och inga tecken på tydligt slitage.</t>
+  </si>
+  <si>
+    <t>Vajrar som håller uppe balansbanor av däck är i gott skick (endast Tybble).</t>
+  </si>
+  <si>
+    <t>Det finns inga skruvar, spikar eller andra vassa föremål som sticker ut.</t>
+  </si>
+  <si>
+    <t>Det finns inte behov av att fylla på med flis i fallutrymmet för att öka den stötdämpande förmågan.</t>
+  </si>
+  <si>
+    <t>Det finns inga vassa, utstickande metalldelar som användare kan sticka eller skära sig på.</t>
+  </si>
+  <si>
+    <t>Material i övriga delar i strukturen är i gott skick.</t>
+  </si>
+  <si>
+    <t>Det behövs inga åtgärder för att förbättra utseendet, som målning eller lagning av detaljer.</t>
+  </si>
+  <si>
+    <t>Fästen för olika metalldelar är i gott skick.</t>
+  </si>
+  <si>
+    <t>Det finns inga delar som sitter löst, är trasiga eller saknas.</t>
+  </si>
+  <si>
+    <t>Fundament är i gott skick.</t>
+  </si>
+  <si>
+    <t>Strukturer som man går på är inte hala på ett sätt som bedöms kräva åtgärder.</t>
+  </si>
+  <si>
+    <t>Plattformarna är i gott skick och det finns inga problem med rötskador.</t>
+  </si>
+  <si>
+    <t>Strukturer som till exempel räcken bedöms klara den belastning som är rimlig att förvänta vid användning.</t>
+  </si>
+  <si>
+    <t>Strukturer som till exempel spångar eller räcken bedöms klara den belastning som är rimlig att förvänta vid användning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Plattformen håller i ett år till utan problem.</t>
+  </si>
+  <si>
+    <t>Strukturen bedöms hålla i ett år till utan problem.</t>
+  </si>
+  <si>
+    <t>Det finns inga vassa, utstickande delar som användare kan sticka eller skära sig på.</t>
+  </si>
+  <si>
+    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet nedanför strukturen. (Bedöms om det finns risk för att barn klättrar upp på och ramlar ner från strukturen).</t>
+  </si>
+  <si>
+    <t>Det finns inga mellanrum mellan lösa delar och plattformen som innebär risk för att fastna eller klämma sig.</t>
+  </si>
+  <si>
+    <t>Det finns inga mellanrum eller öppningar i strukturen som gör att barn kan fastna med hals eller huvud. Det gäller omslutande öppningar mellan 9 och 23 cm i diameter.</t>
+  </si>
+  <si>
+    <t>Hålrum intill trädstam är lagom stort. Trädet växer inte in i plattformen och det är inte heller uppenbar risk att trampa ner med en fot i mellanrummet.</t>
+  </si>
+  <si>
+    <t>Det finns inga öppningar vända uppåt där en smal hals skulle kunna fastna. Det gäller öppningar mellan 4,5 till 9 cm.</t>
+  </si>
+  <si>
+    <t>Fästen för olika balansbanor är i gott skick.</t>
+  </si>
+  <si>
+    <t>Det finns inga öppna vinklar och klykor där barn kan fastna med halsen. Det gäller vinkar som är riktade uppåt eller snett uppåt och som är smalare än 60 grader.</t>
+  </si>
+  <si>
+    <t>Ingående strukturer i balansbanorna är i gott skick. Det kan handla om rep, slacklines, plankor i olika former av hängbroar och liknande delar.</t>
+  </si>
+  <si>
+    <t>Det finns inga springor i tak där snoddar från kläder skulle kunna fastna.</t>
+  </si>
+  <si>
+    <t>Valda material har en god hållfasthet. Aktuella strukturer bedöms hålla i ett år till utan problem och klara av belastning vid användning.</t>
+  </si>
+  <si>
+    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet runt plattformar och balansbanor.</t>
+  </si>
+  <si>
+    <t>Strukturen är inte tydligt sliten. Det behövs inga åtgärder för att förbättra utseendet, som målning eller lagning av detaljer.</t>
+  </si>
+  <si>
     <t>Skulpturer</t>
   </si>
   <si>
     <t>Lekkök och möbler mm</t>
-  </si>
-  <si>
-    <t>Lundbyparken</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>Öknaskogen</t>
-  </si>
-  <si>
-    <t>Hjärstaskogen</t>
-  </si>
-  <si>
-    <t>Japanska dammen (Hjärstaskogen)</t>
-  </si>
-  <si>
-    <t>Baronbackarna</t>
-  </si>
-  <si>
-    <t>Tjäderleken, Björkhaga</t>
-  </si>
-  <si>
-    <t>VOX-parken</t>
-  </si>
-  <si>
-    <t>Militärförråden (Varberga)</t>
-  </si>
-  <si>
-    <t>Myrans lekplats (Varberga)</t>
-  </si>
-  <si>
-    <t>Fantasigläntan (Varberga)</t>
-  </si>
-  <si>
-    <t>Groddammen (Varberga)</t>
-  </si>
-  <si>
-    <t>Östra Rostas cykellek</t>
-  </si>
-  <si>
-    <t>Östra Rostas vattenlek</t>
-  </si>
-  <si>
-    <t>Sköldpaddsleken (Östra Rosta)</t>
-  </si>
-  <si>
-    <t>Bråtenvägen, Lillån</t>
-  </si>
-  <si>
-    <t>Norrbyparken</t>
-  </si>
-  <si>
-    <t>Ringstorp (solrosparken)</t>
-  </si>
-  <si>
-    <t>Sofiaparken</t>
-  </si>
-  <si>
-    <t>Stora holmen</t>
-  </si>
-  <si>
-    <t>Stadsparken</t>
-  </si>
-  <si>
-    <t>Eklunden</t>
-  </si>
-  <si>
-    <t>Hagen</t>
-  </si>
-  <si>
-    <t>Lergöken (Sörbyängen)</t>
-  </si>
-  <si>
-    <t>Tybble naturlek</t>
-  </si>
-  <si>
-    <t>Tybbleparken</t>
-  </si>
-  <si>
-    <t>Hjälmarsviksparken</t>
-  </si>
-  <si>
-    <t>Äventyrsstigen (Saxons)</t>
-  </si>
-  <si>
-    <t>Tallebacka-Majas väg</t>
-  </si>
-  <si>
-    <t>Vänneboparken</t>
-  </si>
-  <si>
-    <t>Brunnsparken</t>
-  </si>
-  <si>
-    <t>Mariebergs skogslek</t>
-  </si>
-  <si>
-    <t>Fästen för vajrar runt träden är i gott skick.</t>
-  </si>
-  <si>
-    <t>Fundament för master utan anmärkning.</t>
-  </si>
-  <si>
-    <t>Det finns inte problem med exponerad ståltråd som sticker fram.</t>
-  </si>
-  <si>
-    <t>Stommar är i gott skick.</t>
-  </si>
-  <si>
-    <t>Trä och andra material är i gott skick.</t>
-  </si>
-  <si>
-    <t>Fundament eller förankring i marken är i gott skick. Det finns inga tecken på att strukturen skulle kunna rasa eller välta.</t>
-  </si>
-  <si>
-    <t>Det finns inga uppenbara problem med erosion.</t>
-  </si>
-  <si>
-    <t>Trappsteg eller ramper intill rutschkanor är väl förankrade och kräver inga åtgärder.</t>
-  </si>
-  <si>
-    <t>Element som är delvis nergrävda har en god förankring. De sitter inte löst eller går att rubba.</t>
-  </si>
-  <si>
-    <t>Skulpturerna är en bra förankring och sitter inte löst.</t>
-  </si>
-  <si>
-    <t>Möbler och andra strukturer är i gott skick.</t>
-  </si>
-  <si>
-    <t>Inga problem med att fästen runt träd växer in i barken eller har för högt tryck.</t>
-  </si>
-  <si>
-    <t>Kättingar i lianer är inte slitna</t>
-  </si>
-  <si>
-    <t>Det finns inga exponerade skruvar eller liknande som däck är fästa med (i varandra eller till annat).</t>
-  </si>
-  <si>
-    <t>Det finns inga problem med röta eller minskad hållfasthet.</t>
-  </si>
-  <si>
-    <t>Förankringen är god och kräver inga åtgärder.</t>
-  </si>
-  <si>
-    <t>Trappsteg är väl förankrade.</t>
-  </si>
-  <si>
-    <t>Stockar och andra träelement är i gott skick. Det finns inte problem med röta.</t>
-  </si>
-  <si>
-    <t>Trä är i gott skick utan större sprickor eller andra skador.</t>
-  </si>
-  <si>
-    <t>Vajrar är bra spända.</t>
-  </si>
-  <si>
-    <t>Fästen av lianer och andra metallfästen är i gott skick.</t>
-  </si>
-  <si>
-    <t>Det samlas inte vatten inne i däck som är förankrade.</t>
-  </si>
-  <si>
-    <t>Stommar bedöms hålla i ett år till utan problem.</t>
-  </si>
-  <si>
-    <t>Det finns inga trasiga eller lösa delar som behöver åtgärdas.</t>
-  </si>
-  <si>
-    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet nedanför strukturen.</t>
-  </si>
-  <si>
-    <t>Målning eller annan utsmyckning kräver inga åtgärder.</t>
-  </si>
-  <si>
-    <t>Vajrar är i gott skick och inga tecken på tydligt slitage.</t>
-  </si>
-  <si>
-    <t>Vajrar som håller uppe balansbanor av däck är i gott skick (endast Tybble).</t>
-  </si>
-  <si>
-    <t>Det finns inga skruvar, spikar eller andra vassa föremål som sticker ut.</t>
-  </si>
-  <si>
-    <t>Det finns inte behov av att fylla på med flis i fallutrymmet för att öka den stötdämpande förmågan.</t>
-  </si>
-  <si>
-    <t>Det finns inga vassa, utstickande metalldelar som användare kan sticka eller skära sig på.</t>
-  </si>
-  <si>
-    <t>Material i övriga delar i strukturen är i gott skick.</t>
-  </si>
-  <si>
-    <t>Det behövs inga åtgärder för att förbättra utseendet, som målning eller lagning av detaljer.</t>
-  </si>
-  <si>
-    <t>Fästen för olika metalldelar är i gott skick.</t>
-  </si>
-  <si>
-    <t>Det finns inga delar som sitter löst, är trasiga eller saknas.</t>
-  </si>
-  <si>
-    <t>Fundament är i gott skick.</t>
-  </si>
-  <si>
-    <t>Strukturer som man går på är inte hala på ett sätt som bedöms kräva åtgärder.</t>
-  </si>
-  <si>
-    <t>Plattformarna är i gott skick och det finns inga problem med rötskador.</t>
-  </si>
-  <si>
-    <t>Strukturer som till exempel räcken bedöms klara den belastning som är rimlig att förvänta vid användning.</t>
-  </si>
-  <si>
-    <t>Strukturer som till exempel spångar eller räcken bedöms klara den belastning som är rimlig att förvänta vid användning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Plattformen håller i ett år till utan problem.</t>
-  </si>
-  <si>
-    <t>Strukturen bedöms hålla i ett år till utan problem.</t>
-  </si>
-  <si>
-    <t>Det finns inga vassa, utstickande delar som användare kan sticka eller skära sig på.</t>
-  </si>
-  <si>
-    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet nedanför strukturen. (Bedöms om det finns risk för att barn klättrar upp på och ramlar ner från strukturen).</t>
-  </si>
-  <si>
-    <t>Det finns inga mellanrum mellan lösa delar och plattformen som innebär risk för att fastna eller klämma sig.</t>
-  </si>
-  <si>
-    <t>Det finns inga mellanrum eller öppningar i strukturen som gör att barn kan fastna med hals eller huvud. Det gäller omslutande öppningar mellan 9 och 23 cm i diameter.</t>
-  </si>
-  <si>
-    <t>Hålrum intill trädstam är lagom stort. Trädet växer inte in i plattformen och det är inte heller uppenbar risk att trampa ner med en fot i mellanrummet.</t>
-  </si>
-  <si>
-    <t>Det finns inga öppningar vända uppåt där en smal hals skulle kunna fastna. Det gäller öppningar mellan 4,5 till 9 cm.</t>
-  </si>
-  <si>
-    <t>Fästen för olika balansbanor är i gott skick.</t>
-  </si>
-  <si>
-    <t>Det finns inga öppna vinklar och klykor där barn kan fastna med halsen. Det gäller vinkar som är riktade uppåt eller snett uppåt och som är smalare än 60 grader.</t>
-  </si>
-  <si>
-    <t>Ingående strukturer i balansbanorna är i gott skick. Det kan handla om rep, slacklines, plankor i olika former av hängbroar och liknande delar.</t>
-  </si>
-  <si>
-    <t>Det finns inga springor i tak där snoddar från kläder skulle kunna fastna.</t>
-  </si>
-  <si>
-    <t>Valda material har en god hållfasthet. Aktuella strukturer bedöms hålla i ett år till utan problem och klara av belastning vid användning.</t>
-  </si>
-  <si>
-    <t>Det finns inga uppstickande stenar, vassa stubbar eller liknande inom fallutrymmet runt plattformar och balansbanor.</t>
-  </si>
-  <si>
-    <t>Strukturen är inte tydligt sliten. Det behövs inga åtgärder för att förbättra utseendet, som målning eller lagning av detaljer.</t>
   </si>
   <si>
     <t>Stock-element</t>
@@ -873,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30" style="13" customWidth="1"/>
@@ -995,7 +998,9 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -1085,10 +1090,10 @@
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="O6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
@@ -1115,9 +1120,7 @@
       <c r="N7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O7" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
@@ -1150,7 +1153,9 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -1175,7 +1180,9 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -1203,8 +1210,12 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="O10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
@@ -1231,7 +1242,9 @@
       <c r="N11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="4"/>
+      <c r="O11" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -1350,9 +1363,7 @@
       <c r="O15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P15" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="P15" s="4"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
@@ -1503,12 +1514,8 @@
       <c r="N20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
@@ -1545,12 +1552,8 @@
       <c r="N21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
@@ -1617,9 +1620,7 @@
         <v>17</v>
       </c>
       <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -1646,9 +1647,7 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="P24" s="4"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
@@ -1738,9 +1737,7 @@
       <c r="O27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P27" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="P27" s="4"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
@@ -1772,7 +1769,9 @@
       <c r="O28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P28" s="4"/>
+      <c r="P28" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
@@ -1785,39 +1784,41 @@
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
+      <c r="L29" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="N29" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="O29" s="4" t="s">
         <v>17</v>
       </c>
       <c r="P29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
     </row>
     <row r="30" spans="1:20" ht="14.25" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1831,16 +1832,18 @@
         <v>17</v>
       </c>
       <c r="P30" s="4"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
     </row>
     <row r="31" spans="1:20" ht="14.25" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
@@ -1853,16 +1856,16 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
-      <c r="M31" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+      <c r="O31" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="P31" s="4"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
     </row>
     <row r="32" spans="1:20" ht="14.25" customHeight="1">
       <c r="A32" s="4" t="s">
@@ -1875,68 +1878,98 @@
         <v>17</v>
       </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="M32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
     </row>
     <row r="33" spans="1:20" ht="14.25" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
+      <c r="A33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
     </row>
     <row r="34" spans="1:20" ht="14.25" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.25" customHeight="1">
+      <c r="A35" s="12"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2002,7 +2035,7 @@
         <v>14</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
@@ -2019,49 +2052,49 @@
     </row>
     <row r="2" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A2" s="20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="29" t="s">
         <v>55</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>58</v>
       </c>
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
@@ -2078,48 +2111,48 @@
     </row>
     <row r="3" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A3" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K3" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="O3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30" t="s">
+        <v>54</v>
+      </c>
       <c r="P3" s="18"/>
       <c r="Q3" s="18"/>
       <c r="R3" s="18"/>
@@ -2150,7 +2183,7 @@
         <v>71</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>71</v>
@@ -2171,9 +2204,7 @@
       <c r="M4" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="29" t="s">
-        <v>73</v>
-      </c>
+      <c r="N4" s="29"/>
       <c r="O4" s="29"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
@@ -2190,39 +2221,39 @@
     </row>
     <row r="5" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A5" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>75</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="20" t="s">
         <v>76</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>77</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="30"/>
@@ -2241,36 +2272,36 @@
     </row>
     <row r="6" spans="1:27" s="15" customFormat="1" ht="60.75">
       <c r="A6" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="F6" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K6" s="20"/>
       <c r="L6" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M6" s="29"/>
       <c r="N6" s="29"/>
@@ -2290,18 +2321,18 @@
     </row>
     <row r="7" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A7" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
@@ -2327,16 +2358,16 @@
     </row>
     <row r="8" spans="1:27" s="15" customFormat="1" ht="45.75">
       <c r="A8" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
       <c r="D8" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
@@ -2362,16 +2393,16 @@
     </row>
     <row r="9" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A9" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
       <c r="D9" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="30"/>
@@ -2397,16 +2428,16 @@
     </row>
     <row r="10" spans="1:27" s="15" customFormat="1" ht="30.75">
       <c r="A10" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
@@ -2432,16 +2463,16 @@
     </row>
     <row r="11" spans="1:27" s="15" customFormat="1" ht="121.5">
       <c r="A11" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="30"/>
@@ -2467,12 +2498,12 @@
     </row>
     <row r="12" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -2500,12 +2531,12 @@
     </row>
     <row r="13" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="29"/>
@@ -2533,12 +2564,12 @@
     </row>
     <row r="14" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="30"/>
@@ -2566,12 +2597,12 @@
     </row>
     <row r="15" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="29"/>
@@ -2599,12 +2630,12 @@
     </row>
     <row r="16" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
       <c r="D16" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="29"/>
@@ -2631,12 +2662,12 @@
     </row>
     <row r="17" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
       <c r="D17" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="29"/>
@@ -2664,12 +2695,12 @@
     </row>
     <row r="18" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
       <c r="D18" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="30"/>
@@ -2700,7 +2731,7 @@
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="29"/>
@@ -2816,10 +2847,10 @@
         <v>13</v>
       </c>
       <c r="N1" s="26" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15">
@@ -2860,13 +2891,13 @@
         <v>12</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="P2" s="3"/>
     </row>

--- a/data/lekplatskontroll.xlsx
+++ b/data/lekplatskontroll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orebrokommun-my.sharepoint.com/personal/mimmi_beckman_orebro_se/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{082FFA92-712D-4D65-A6DC-D1B3836D4844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1048D69-7278-4DA7-A134-A28402493461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="104">
   <si>
     <t>Lekplats</t>
   </si>
@@ -85,7 +85,7 @@
     <t>Träd</t>
   </si>
   <si>
-    <t>Portaler</t>
+    <t>Portal</t>
   </si>
   <si>
     <t>Lundbyparken</t>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>Mariebergs skogslek</t>
-  </si>
-  <si>
-    <t>Portal</t>
   </si>
   <si>
     <t>Fästen för vajrar runt träden är i gott skick.</t>
@@ -2035,7 +2032,7 @@
         <v>14</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
@@ -2052,49 +2049,49 @@
     </row>
     <row r="2" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="I2" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="K2" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="29" t="s">
         <v>54</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>55</v>
       </c>
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
@@ -2111,47 +2108,47 @@
     </row>
     <row r="3" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="F3" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="20" t="s">
+      <c r="L3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="20" t="s">
         <v>65</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>66</v>
       </c>
       <c r="N3" s="30"/>
       <c r="O3" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P3" s="18"/>
       <c r="Q3" s="18"/>
@@ -2168,41 +2165,41 @@
     </row>
     <row r="4" spans="1:27" s="15" customFormat="1" ht="60.75">
       <c r="A4" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>71</v>
-      </c>
       <c r="F4" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="20" t="s">
         <v>71</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>72</v>
       </c>
       <c r="N4" s="29"/>
       <c r="O4" s="29"/>
@@ -2221,39 +2218,39 @@
     </row>
     <row r="5" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>73</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>74</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="30"/>
@@ -2272,36 +2269,36 @@
     </row>
     <row r="6" spans="1:27" s="15" customFormat="1" ht="60.75">
       <c r="A6" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>79</v>
-      </c>
       <c r="F6" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K6" s="20"/>
       <c r="L6" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M6" s="29"/>
       <c r="N6" s="29"/>
@@ -2321,18 +2318,18 @@
     </row>
     <row r="7" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A7" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
@@ -2358,16 +2355,16 @@
     </row>
     <row r="8" spans="1:27" s="15" customFormat="1" ht="45.75">
       <c r="A8" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
       <c r="D8" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
@@ -2393,16 +2390,16 @@
     </row>
     <row r="9" spans="1:27" s="15" customFormat="1" ht="76.5">
       <c r="A9" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
       <c r="D9" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="30"/>
@@ -2428,16 +2425,16 @@
     </row>
     <row r="10" spans="1:27" s="15" customFormat="1" ht="30.75">
       <c r="A10" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
@@ -2463,16 +2460,16 @@
     </row>
     <row r="11" spans="1:27" s="15" customFormat="1" ht="121.5">
       <c r="A11" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="30"/>
@@ -2498,12 +2495,12 @@
     </row>
     <row r="12" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
       <c r="D12" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -2531,12 +2528,12 @@
     </row>
     <row r="13" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="29"/>
@@ -2564,12 +2561,12 @@
     </row>
     <row r="14" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="30"/>
@@ -2597,12 +2594,12 @@
     </row>
     <row r="15" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="D15" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="29"/>
@@ -2630,12 +2627,12 @@
     </row>
     <row r="16" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
       <c r="D16" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="29"/>
@@ -2662,12 +2659,12 @@
     </row>
     <row r="17" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
       <c r="D17" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="29"/>
@@ -2695,12 +2692,12 @@
     </row>
     <row r="18" spans="1:27" s="15" customFormat="1" ht="14.25" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
       <c r="D18" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="30"/>
@@ -2731,7 +2728,7 @@
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="29"/>
@@ -2847,10 +2844,10 @@
         <v>13</v>
       </c>
       <c r="N1" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="O1" s="26" t="s">
         <v>102</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15">
@@ -2891,13 +2888,13 @@
         <v>12</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="P2" s="3"/>
     </row>
